--- a/supplementary/multiple_splits_results.xlsx
+++ b/supplementary/multiple_splits_results.xlsx
@@ -425,13 +425,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Modelo</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -441,23 +446,43 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_F1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_F2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_F3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>split</t>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>N_descriptors</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -468,17 +493,29 @@
         <v>0.8954257818897899</v>
       </c>
       <c r="D2" t="n">
+        <v>0.939751195387535</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8965280434820532</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8954257818897899</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9362090940047649</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.09698684737824717</v>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>0.1324245792089869</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
+      <c r="J2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,18 +527,30 @@
         <v>0.8689994369309739</v>
       </c>
       <c r="D3" t="n">
+        <v>0.9340470927549935</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8703802446658562</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8689994369309739</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9200888636312624</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.09879732176661489</v>
       </c>
-      <c r="E3" t="n">
+      <c r="I3" t="n">
         <v>0.1482152427780387</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="J3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
+      <c r="A4" t="n">
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -512,18 +561,30 @@
         <v>0.856447241777934</v>
       </c>
       <c r="D4" t="n">
+        <v>0.9264989277203269</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8579603555712866</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.856447241777934</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9124319486142403</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.102263519269348</v>
       </c>
-      <c r="E4" t="n">
+      <c r="I4" t="n">
         <v>0.1551536723029553</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
+      <c r="J4" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
+      <c r="A5" t="n">
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -534,62 +595,98 @@
         <v>0.8419590601413226</v>
       </c>
       <c r="D5" t="n">
+        <v>0.9089427306778824</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8456715603219047</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8419590601413226</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8531995267946508</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.1318100818452382</v>
       </c>
-      <c r="E5" t="n">
+      <c r="I5" t="n">
         <v>0.1940386972666215</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
+      <c r="J5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
+      <c r="A6" t="n">
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8216814685950379</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8999240552500194</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.82587030460572</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8216814685950379</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8343641539025303</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1384197198599577</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2061112929680595</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>0.8262830513248393</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
+        <v>0.9032651588426629</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8303637927068092</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8262830513248393</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.838638454744024</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.1294367067188965</v>
       </c>
-      <c r="E6" t="n">
+      <c r="I7" t="n">
         <v>0.2034345181200096</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.8216814685950379</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.1384197198599577</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.2061112929680595</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="J7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
+      <c r="A8" t="n">
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -600,62 +697,98 @@
         <v>0.9440550131478616</v>
       </c>
       <c r="D8" t="n">
+        <v>0.9719305726697717</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9472452762533321</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9440550131478616</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9419637099593722</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.09126227083333308</v>
       </c>
-      <c r="E8" t="n">
+      <c r="I8" t="n">
         <v>0.1203038085111671</v>
       </c>
-      <c r="F8" t="n">
-        <v>2</v>
+      <c r="J8" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
+      <c r="A9" t="n">
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9314491543585575</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9670709272997046</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9353582666133642</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9314491543585575</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9288866262370924</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1007575434446335</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1331696310288905</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>0.9355045657630221</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
+        <v>0.968196296329601</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9391824181658003</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9355045657630221</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9330936346885491</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.08948827884183666</v>
       </c>
-      <c r="E9" t="n">
+      <c r="I10" t="n">
         <v>0.1291704800865195</v>
       </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.9314491543585575</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1007575434446335</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.1331696310288905</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
+      <c r="J10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
+      <c r="A11" t="n">
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -666,62 +799,98 @@
         <v>0.9662666356108672</v>
       </c>
       <c r="D11" t="n">
+        <v>0.9821061442512001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9673462075864792</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9662666356108672</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9657774404618481</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.06529544409138324</v>
       </c>
-      <c r="E11" t="n">
+      <c r="I11" t="n">
         <v>0.09280432013257092</v>
       </c>
-      <c r="F11" t="n">
-        <v>3</v>
+      <c r="J11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
+      <c r="A12" t="n">
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9580121815604304</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9785415831953317</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9593559215912659</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9580121815604304</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9574032818117546</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.07513337090611455</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1035380592139608</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>0.9643528326074757</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
+        <v>0.9824699755059239</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.965493652197333</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9643528326074757</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9638358838334509</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.06802037198501251</v>
       </c>
-      <c r="E12" t="n">
+      <c r="I13" t="n">
         <v>0.09540054977633616</v>
       </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.9580121815604304</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.07513337090611455</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.1035380592139608</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
+      <c r="J13" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
+      <c r="A14" t="n">
+        <v>5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -732,84 +901,132 @@
         <v>0.9009827004646178</v>
       </c>
       <c r="D14" t="n">
+        <v>0.9474342693259316</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9152241958186075</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9009827004646178</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9538357680316485</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.08595235227272932</v>
       </c>
-      <c r="E14" t="n">
+      <c r="I14" t="n">
         <v>0.1137213653095646</v>
       </c>
-      <c r="F14" t="n">
-        <v>4</v>
+      <c r="J14" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
+      <c r="A15" t="n">
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8724629529865153</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.934078475556011</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8908063967183358</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8724629529865153</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9405391800168696</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.09557310700416569</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1290638763582509</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C16" t="n">
         <v>0.8803399737200521</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
+        <v>0.9375831867549432</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8975504785138656</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8803399737200521</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9442116353763754</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.09478243808578798</v>
       </c>
-      <c r="E15" t="n">
+      <c r="I16" t="n">
         <v>0.1250146971468147</v>
       </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.8724629529865153</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.09557310700416569</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.1290638763582509</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
+      <c r="J16" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
+      <c r="A17" t="n">
+        <v>6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LightGBMRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9145506239665533</v>
+        <v>0.894049393318599</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09619538782987876</v>
+        <v>0.9462626780794646</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1311064822896473</v>
+        <v>0.9052719799594063</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>0.894049393318599</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9186922674654702</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1016956134259239</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1459894394603449</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
+      <c r="A18" t="n">
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -820,106 +1037,166 @@
         <v>0.9035070822584135</v>
       </c>
       <c r="D18" t="n">
+        <v>0.9480651565861515</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9137278838517029</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9035070822584135</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9259502083758567</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.1027878798544407</v>
       </c>
-      <c r="E18" t="n">
+      <c r="I18" t="n">
         <v>0.1393212737964951</v>
       </c>
-      <c r="F18" t="n">
-        <v>5</v>
+      <c r="J18" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
+      <c r="A19" t="n">
+        <v>6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>LightGBMRegressor</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9145506239665533</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9544231876686563</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9236016625209802</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9145506239665533</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9344251512153958</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.09619538782987876</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1311064822896473</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>RandomForestRegressor</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0.894049393318599</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1016956134259239</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.1459894394603449</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="n">
+        <v>0.9240840964653053</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9594629634413807</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9246651832685314</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9240840964653053</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9336216594456638</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.09548918646089744</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1313707152601762</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>XGBoostRegressor</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>0.9429777762598368</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
+        <v>0.9690654232937554</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9434142442482719</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9429777762598368</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9501416645214492</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.08180692791938782</v>
       </c>
-      <c r="E20" t="n">
+      <c r="I21" t="n">
         <v>0.1138555634159965</v>
       </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>0.9276673490355964</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
+        <v>0.9619571372890819</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9282210083739005</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9276673490355964</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9367547362889669</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.09080288984046755</v>
       </c>
-      <c r="E21" t="n">
+      <c r="I22" t="n">
         <v>0.1282328731025865</v>
       </c>
-      <c r="F21" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>RandomForestRegressor</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.9240840964653053</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.09548918646089744</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.1313707152601762</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6</v>
+      <c r="J22" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
+      <c r="A23" t="n">
+        <v>8</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -930,304 +1207,472 @@
         <v>0.9485224486371104</v>
       </c>
       <c r="D23" t="n">
+        <v>0.9734308968556326</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9492457359381945</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9485224486371104</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.949328834360246</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.0815378108797041</v>
       </c>
-      <c r="E23" t="n">
+      <c r="I23" t="n">
         <v>0.1134418176758812</v>
       </c>
-      <c r="F23" t="n">
+      <c r="J23" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9389580203090458</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.9687523884494291</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9398156929755691</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9389580203090458</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9399142309218568</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.08804098375141624</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1235317350555806</v>
+      </c>
+      <c r="J24" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LightGBMRegressor</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9406479548618646</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.9691867461430065</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9414818830384237</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9406479548618646</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9415776929820968</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.08222178642216263</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.121809758023974</v>
+      </c>
+      <c r="J25" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.849571053400247</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.925721647914318</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8681951738994279</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.849571053400247</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9061200863394991</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1100881770833327</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1592833743807415</v>
+      </c>
+      <c r="J26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8875272703663759</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.9426669650869861</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.901452154618486</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.8875272703663759</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.9298078568929976</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0985783489048481</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1377299399182727</v>
+      </c>
+      <c r="J27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LightGBMRegressor</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8637495874210226</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9288861718654986</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8806183095605563</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.8637495874210226</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.9149686462728776</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1083470316540223</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.151591082212131</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7318727294834568</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.8638417453392251</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7673449415364132</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.7318727294834568</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.7841769240665819</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1685174223856245</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2363186097226798</v>
+      </c>
+      <c r="J29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.666656361608672</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.81567351962711</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.710756449618152</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.666656361608672</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.731682460937838</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1772470299899578</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.2634956895373368</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LightGBMRegressor</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7634040591651021</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.8700708042201629</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7947047969378622</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.7634040591651021</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.809557365776421</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1549901294081915</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2219888053904578</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8366618743572012</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.9097603598816657</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8370717358172267</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8366618743572012</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.8808021837204874</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1293661696623089</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1787853084597701</v>
+      </c>
+      <c r="J32" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8283029040078144</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.8965936845951663</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8287337404837968</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.8283029040078144</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.8747021320144266</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1264979718625546</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1833029773616421</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.9406479548618646</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.08222178642216263</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.121809758023974</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="C34" t="n">
+        <v>0.8646297092178192</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.924913802679636</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8649693914861551</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8646297092178192</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9012120226869398</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1219960920297765</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.162760766042482</v>
+      </c>
+      <c r="J34" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RandomForestRegressor</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.9111958894510076</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.9498754250659631</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9115819879952924</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9111958894510076</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9392517134726265</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1004497230581234</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1282416919682393</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>XGBoostRegressor</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>0.9389580203090458</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.08804098375141624</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.1235317350555806</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.8875272703663759</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0985783489048481</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.1377299399182727</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>LightGBMRegressor</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.8637495874210226</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.1083470316540223</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.151591082212131</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>RandomForestRegressor</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.849571053400247</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.1100881770833327</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.1592833743807415</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>LightGBMRegressor</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.7634040591651021</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.1549901294081915</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.2219888053904578</v>
-      </c>
-      <c r="F29" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>RandomForestRegressor</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.7318727294834568</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.1685174223856245</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.2363186097226798</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.666656361608672</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.1772470299899578</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.2634956895373368</v>
-      </c>
-      <c r="F31" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LightGBMRegressor</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.8646297092178192</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.1219960920297765</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.162760766042482</v>
-      </c>
-      <c r="F32" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>RandomForestRegressor</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.8366618743572012</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.1293661696623089</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.1787853084597701</v>
-      </c>
-      <c r="F33" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.8283029040078144</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.1264979718625546</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.1833029773616421</v>
-      </c>
-      <c r="F34" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
+      <c r="C36" t="n">
         <v>0.9146345081517133</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D36" t="n">
+        <v>0.9550742843472704</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9150056564232407</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9146345081517133</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.941603971637226</v>
+      </c>
+      <c r="H36" t="n">
         <v>0.09074156865477562</v>
       </c>
-      <c r="E35" t="n">
+      <c r="I36" t="n">
         <v>0.125734331867169</v>
       </c>
-      <c r="F35" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>RandomForestRegressor</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.9111958894510076</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.1004497230581234</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.1282416919682393</v>
-      </c>
-      <c r="F36" t="n">
-        <v>11</v>
+      <c r="J36" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
+      <c r="A37" t="n">
+        <v>12</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1238,40 +1683,64 @@
         <v>0.9110149646271279</v>
       </c>
       <c r="D37" t="n">
+        <v>0.9521448719219923</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9114018497882788</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9110149646271279</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.9391279481089174</v>
+      </c>
+      <c r="H37" t="n">
         <v>0.09377167223340746</v>
       </c>
-      <c r="E37" t="n">
+      <c r="I37" t="n">
         <v>0.1283722619369363</v>
       </c>
-      <c r="F37" t="n">
-        <v>11</v>
+      <c r="J37" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>36</v>
+      <c r="A38" t="n">
+        <v>13</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LightGBMRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7908115282720641</v>
+        <v>0.7540097157771452</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1580414980188323</v>
+        <v>0.8483550998891086</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2846929457696287</v>
+        <v>0.8197966255433221</v>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>0.7540097157771452</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.5036790021689348</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.166115856959953</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.3087214531291033</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>37</v>
+      <c r="A39" t="n">
+        <v>13</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1282,128 +1751,200 @@
         <v>0.7744481445612734</v>
       </c>
       <c r="D39" t="n">
+        <v>0.8600608801619498</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8347690617398499</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.7744481445612734</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5449164900651957</v>
+      </c>
+      <c r="H39" t="n">
         <v>0.1603559052944183</v>
       </c>
-      <c r="E39" t="n">
+      <c r="I39" t="n">
         <v>0.2956181090355166</v>
       </c>
-      <c r="F39" t="n">
-        <v>12</v>
+      <c r="J39" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
+      <c r="A40" t="n">
+        <v>13</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>LightGBMRegressor</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7908115282720641</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8742236605377317</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8467562707937754</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.7908115282720641</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5779319847904856</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1580414980188323</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2846929457696287</v>
+      </c>
+      <c r="J40" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>14</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>RandomForestRegressor</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>0.7540097157771452</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.166115856959953</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.3087214531291033</v>
-      </c>
-      <c r="F40" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="n">
+        <v>0.9574482753256236</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.978912021873235</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9574803922120595</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9574482753256236</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.9343822652365781</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0890739797794121</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1225526783262517</v>
+      </c>
+      <c r="J41" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>14</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.9560540992846855</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.9778629609831477</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9560872684573432</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.9560540992846855</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.9322323482974212</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.091312999650836</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1245441716405762</v>
+      </c>
+      <c r="J42" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>14</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C43" t="n">
         <v>0.960653163301506</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D43" t="n">
+        <v>0.9803681232888337</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9606828612255156</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.960653163301506</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.9393244265886083</v>
+      </c>
+      <c r="H43" t="n">
         <v>0.08324022908365609</v>
       </c>
-      <c r="E41" t="n">
+      <c r="I43" t="n">
         <v>0.1178471637576725</v>
       </c>
-      <c r="F41" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="J43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>15</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>RandomForestRegressor</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>0.9574482753256236</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.0890739797794121</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.1225526783262517</v>
-      </c>
-      <c r="F42" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>0.9560540992846855</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.091312999650836</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.1245441716405762</v>
-      </c>
-      <c r="F43" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>LightGBMRegressor</t>
-        </is>
-      </c>
       <c r="C44" t="n">
-        <v>0.8377608577722451</v>
+        <v>0.8131336692891687</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1134934996225749</v>
+        <v>0.9110714123067591</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1706919033322059</v>
+        <v>0.8333830646447016</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>0.8131336692891687</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8747452961583455</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1224511994949501</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1831895219435427</v>
+      </c>
+      <c r="J44" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>43</v>
+      <c r="A45" t="n">
+        <v>15</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1414,62 +1955,98 @@
         <v>0.8189669593289162</v>
       </c>
       <c r="D45" t="n">
+        <v>0.9120578165307837</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.8385842419020713</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.8189669593289162</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.8786552943563712</v>
+      </c>
+      <c r="H45" t="n">
         <v>0.126547054797411</v>
       </c>
-      <c r="E45" t="n">
+      <c r="I45" t="n">
         <v>0.1803075961137559</v>
       </c>
-      <c r="F45" t="n">
-        <v>14</v>
+      <c r="J45" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>44</v>
+      <c r="A46" t="n">
+        <v>15</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>LightGBMRegressor</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.8377608577722451</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.9217847705776322</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.8553415772127961</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.8377608577722451</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.8912526636876719</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1134934996225749</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1706919033322059</v>
+      </c>
+      <c r="J46" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>16</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>RandomForestRegressor</t>
         </is>
       </c>
-      <c r="C46" t="n">
-        <v>0.8131336692891687</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.1224511994949501</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.1831895219435427</v>
-      </c>
-      <c r="F46" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>LightGBMRegressor</t>
-        </is>
-      </c>
       <c r="C47" t="n">
-        <v>0.9439269667159218</v>
+        <v>0.8814541845914914</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09024150053009079</v>
+        <v>0.9382410496325285</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1138821540470307</v>
+        <v>0.8814722509234543</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>0.8814541845914914</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.8942812053870164</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.1324520204838565</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.1655852935197128</v>
+      </c>
+      <c r="J47" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46</v>
+      <c r="A48" t="n">
+        <v>16</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1480,172 +2057,268 @@
         <v>0.9323107804572389</v>
       </c>
       <c r="D48" t="n">
+        <v>0.9686542101597478</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.932321096265573</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.9323107804572389</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.9396349616079261</v>
+      </c>
+      <c r="H48" t="n">
         <v>0.09496941179037097</v>
       </c>
-      <c r="E48" t="n">
+      <c r="I48" t="n">
         <v>0.125123360939139</v>
       </c>
-      <c r="F48" t="n">
-        <v>15</v>
+      <c r="J48" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>47</v>
+      <c r="A49" t="n">
+        <v>16</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>LightGBMRegressor</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.9439269667159218</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.9730703812010189</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9439355122223995</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9439269667159218</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.949994240887722</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.09024150053009079</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.1138821540470307</v>
+      </c>
+      <c r="J49" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>17</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>RandomForestRegressor</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>0.8814541845914914</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.1324520204838565</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.1655852935197128</v>
-      </c>
-      <c r="F49" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="n">
+        <v>0.9253043739325341</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.9627000524417576</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9267237443372209</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.9253043739325341</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.9142353237759904</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1102453265867094</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1451317775530209</v>
+      </c>
+      <c r="J50" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>17</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>XGBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.8910098366371992</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.9465902595779283</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.893080873730314</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.8910098366371992</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8748587224642879</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.1262148080021143</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1753107631928736</v>
+      </c>
+      <c r="J51" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>17</v>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C52" t="n">
         <v>0.9373347508572804</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D52" t="n">
+        <v>0.9689458456116735</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9385255193763791</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.9373347508572804</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.9280484670097287</v>
+      </c>
+      <c r="H52" t="n">
         <v>0.1021544692765979</v>
       </c>
-      <c r="E50" t="n">
+      <c r="I52" t="n">
         <v>0.1329316250657933</v>
       </c>
-      <c r="F50" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="J52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>18</v>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>RandomForestRegressor</t>
         </is>
       </c>
-      <c r="C51" t="n">
-        <v>0.9253043739325341</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.1102453265867094</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.1451317775530209</v>
-      </c>
-      <c r="F51" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="C53" t="n">
+        <v>0.8120270964936833</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.8871070087214087</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8179087426218945</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.8120270964936833</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.7801101464887754</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1174475888480388</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.2316245773209281</v>
+      </c>
+      <c r="J53" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>18</v>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>XGBoostRegressor</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>0.8910098366371992</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.1262148080021143</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.1753107631928736</v>
-      </c>
-      <c r="F52" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="C54" t="n">
+        <v>0.7819189594244106</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.8689900793098486</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.7887426849934237</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.7819189594244106</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.7448897837334818</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1241565296798945</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.2494858795044657</v>
+      </c>
+      <c r="J54" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>18</v>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>LightGBMRegressor</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C55" t="n">
         <v>0.8374305543336733</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D55" t="n">
+        <v>0.9041274181434322</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8425173297828628</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.8374305543336733</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.8098269967311096</v>
+      </c>
+      <c r="H55" t="n">
         <v>0.1178358879359953</v>
       </c>
-      <c r="E53" t="n">
+      <c r="I55" t="n">
         <v>0.2154053459009258</v>
       </c>
-      <c r="F53" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>RandomForestRegressor</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.8120270964936833</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.1174475888480388</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.2316245773209281</v>
-      </c>
-      <c r="F54" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>XGBoostRegressor</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.7819189594244106</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.1241565296798945</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.2494858795044657</v>
-      </c>
-      <c r="F55" t="n">
-        <v>17</v>
+      <c r="J55" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>54</v>
+      <c r="A56" t="n">
+        <v>19</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1656,18 +2329,30 @@
         <v>0.9608988530728813</v>
       </c>
       <c r="D56" t="n">
+        <v>0.9808989461529255</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9612604531583623</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.9608988530728813</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.9451671122224722</v>
+      </c>
+      <c r="H56" t="n">
         <v>0.08502171351001345</v>
       </c>
-      <c r="E56" t="n">
+      <c r="I56" t="n">
         <v>0.1133689226759322</v>
       </c>
-      <c r="F56" t="n">
-        <v>18</v>
+      <c r="J56" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>55</v>
+      <c r="A57" t="n">
+        <v>19</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1678,18 +2363,30 @@
         <v>0.9527748336885902</v>
       </c>
       <c r="D57" t="n">
+        <v>0.9757447546998552</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9532115631841953</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.9527748336885902</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.9337745194672877</v>
+      </c>
+      <c r="H57" t="n">
         <v>0.09333012782037259</v>
       </c>
-      <c r="E57" t="n">
+      <c r="I57" t="n">
         <v>0.1245908129039481</v>
       </c>
-      <c r="F57" t="n">
-        <v>18</v>
+      <c r="J57" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>56</v>
+      <c r="A58" t="n">
+        <v>19</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1700,40 +2397,64 @@
         <v>0.9478014336247195</v>
       </c>
       <c r="D58" t="n">
+        <v>0.9733906572283813</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9482841561928955</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.9478014336247195</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9268001489179207</v>
+      </c>
+      <c r="H58" t="n">
         <v>0.09922622568627924</v>
       </c>
-      <c r="E58" t="n">
+      <c r="I58" t="n">
         <v>0.1309871096326218</v>
       </c>
-      <c r="F58" t="n">
-        <v>18</v>
+      <c r="J58" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>57</v>
+      <c r="A59" t="n">
+        <v>20</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LightGBMRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.9619726484108116</v>
+        <v>0.9300661096720469</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0681165194725968</v>
+        <v>0.9620908578306994</v>
       </c>
       <c r="E59" t="n">
-        <v>0.08705350480299431</v>
+        <v>0.9326135516698083</v>
       </c>
       <c r="F59" t="n">
-        <v>19</v>
+        <v>0.9300661096720469</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.9475771997210114</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.08035764547350663</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1180543691167202</v>
+      </c>
+      <c r="J59" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>58</v>
+      <c r="A60" t="n">
+        <v>20</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1744,35 +2465,59 @@
         <v>0.9379461088118755</v>
       </c>
       <c r="D60" t="n">
+        <v>0.9668659379775512</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9402065105683891</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.9379461088118755</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.9534840871995808</v>
+      </c>
+      <c r="H60" t="n">
         <v>0.07505634784698489</v>
       </c>
-      <c r="E60" t="n">
+      <c r="I60" t="n">
         <v>0.1112045944239629</v>
       </c>
-      <c r="F60" t="n">
-        <v>19</v>
+      <c r="J60" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>59</v>
+      <c r="A61" t="n">
+        <v>20</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>LightGBMRegressor</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.9300661096720469</v>
+        <v>0.9619726484108116</v>
       </c>
       <c r="D61" t="n">
-        <v>0.08035764547350663</v>
+        <v>0.980373594175968</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1180543691167202</v>
+        <v>0.9633578490917355</v>
       </c>
       <c r="F61" t="n">
-        <v>19</v>
+        <v>0.9619726484108116</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.9714945036211995</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.0681165194725968</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.08705350480299431</v>
+      </c>
+      <c r="J61" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
